--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487402_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487402_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>16.3879</v>
+        <v>14.0555</v>
       </c>
       <c r="E2" t="n">
-        <v>11.8045</v>
+        <v>10.1671</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5834</v>
+        <v>3.8884</v>
       </c>
       <c r="G2" t="n">
         <v>5.6902</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8936</v>
+        <v>1.5612</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2714</v>
+        <v>0.634</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6222</v>
+        <v>0.9272</v>
       </c>
       <c r="V2" t="n">
         <v>4.2581</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>11.0858</v>
+        <v>10.8666</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4435</v>
+        <v>7.1598</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6424</v>
+        <v>3.7068</v>
       </c>
       <c r="G3" t="n">
         <v>7.168</v>
@@ -688,13 +688,13 @@
         <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7796</v>
+        <v>0.5604</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6358</v>
+        <v>0.0806</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4154</v>
+        <v>0.4798</v>
       </c>
       <c r="V3" t="n">
         <v>1.7673</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.6035</v>
+        <v>7.9907</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6777</v>
+        <v>6.9847</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9258</v>
+        <v>1.006</v>
       </c>
       <c r="G4" t="n">
         <v>8.4102</v>
@@ -766,13 +766,13 @@
         <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5694</v>
+        <v>-0.1822</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5346</v>
+        <v>-0.2276</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0348</v>
+        <v>0.0454</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2166</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>7.2106</v>
+        <v>7.4779</v>
       </c>
       <c r="E5" t="n">
         <v>4.5247</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6859</v>
+        <v>2.9532</v>
       </c>
       <c r="G5" t="n">
         <v>4.6091</v>
@@ -844,13 +844,13 @@
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0241</v>
+        <v>0.2432</v>
       </c>
       <c r="T5" t="n">
         <v>-0.2088</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1847</v>
+        <v>0.452</v>
       </c>
       <c r="V5" t="n">
         <v>0.2754</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5493</v>
+        <v>3.8655</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9092</v>
+        <v>-0.8069</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4585</v>
+        <v>4.6724</v>
       </c>
       <c r="G6" t="n">
         <v>1.9349</v>
@@ -922,13 +922,13 @@
         <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.202</v>
+        <v>0.5181</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2247</v>
+        <v>0.327</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0227</v>
+        <v>0.1911</v>
       </c>
       <c r="V6" t="n">
         <v>1.2166</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>A. ALVAREZ JORGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4405</v>
+        <v>3.4387</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9434</v>
+        <v>-1.4336</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4971</v>
+        <v>4.8724</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2638</v>
+        <v>0.0525</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6016</v>
+        <v>-0.2052</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6622</v>
+        <v>0.2577</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5004</v>
+        <v>-2.7473</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2579</v>
+        <v>-0.8218</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2425</v>
+        <v>-1.9255</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7634</v>
+        <v>2.7998</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3437</v>
+        <v>0.6166</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4197</v>
+        <v>2.1832</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1751</v>
+        <v>2.1543</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1366</v>
+        <v>0.0153</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0882</v>
+        <v>0.097</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2248</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8825</v>
+        <v>1.2166</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6659</v>
+        <v>1.2166</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALVAREZ JORGE</t>
+          <t>S. NIETO FONTAIÑA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.397</v>
+        <v>2.8753</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0476</v>
+        <v>-0.2475</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4447</v>
+        <v>3.1228</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0525</v>
+        <v>2.7609</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2052</v>
+        <v>1.9834</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2577</v>
+        <v>0.7775</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7473</v>
+        <v>1.185</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8218</v>
+        <v>1.3678</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9255</v>
+        <v>-0.1828</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7998</v>
+        <v>1.5759</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6166</v>
+        <v>0.6156</v>
       </c>
       <c r="O8" t="n">
-        <v>2.1832</v>
+        <v>0.9603</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1543</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>-1.9585</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.9585</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.0823</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.1967</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.1543</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-1.0264</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.517</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.5094</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.2166</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. NIETO FONTAIÑA</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0963</v>
+        <v>2.5788</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7592</v>
+        <v>1.8411</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8555</v>
+        <v>0.7377</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7609</v>
+        <v>4.2638</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9834</v>
+        <v>3.6016</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7775</v>
+        <v>0.6622</v>
       </c>
       <c r="J9" t="n">
-        <v>1.185</v>
+        <v>3.5004</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3678</v>
+        <v>3.2579</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1828</v>
+        <v>0.2425</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5759</v>
+        <v>0.7634</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6156</v>
+        <v>0.3437</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9603</v>
+        <v>0.4197</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6646</v>
+        <v>0.0016</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.594</v>
+        <v>-0.0141</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0706</v>
+        <v>0.0157</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.8825</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6083</v>
+        <v>-0.6659</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0787</v>
+        <v>2.2658</v>
       </c>
       <c r="E10" t="n">
         <v>-0.3035</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3822</v>
+        <v>2.5693</v>
       </c>
       <c r="G10" t="n">
         <v>1.5429</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.083</v>
+        <v>0.2701</v>
       </c>
       <c r="T10" t="n">
         <v>0.0882</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0052</v>
+        <v>0.1819</v>
       </c>
       <c r="V10" t="n">
         <v>2.2154</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. PULLEIRO GONZALEZ</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7746</v>
+        <v>1.5889</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6619</v>
+        <v>0.2172</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4365</v>
+        <v>1.3718</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4511</v>
+        <v>1.282</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8504</v>
+        <v>1.2216</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3993</v>
+        <v>0.0604</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.4822</v>
+        <v>0.1759</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.9212</v>
+        <v>1.4903</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-1.3144</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0311</v>
+        <v>1.1061</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0708</v>
+        <v>-0.2687</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9603</v>
+        <v>1.3749</v>
       </c>
       <c r="P11" t="n">
         <v>1.3709</v>
@@ -1312,28 +1312,28 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5217</v>
+        <v>-0.1228</v>
       </c>
       <c r="T11" t="n">
-        <v>2.212</v>
+        <v>-0.2341</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3098</v>
+        <v>0.1113</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3329</v>
+        <v>-0.9412</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>R. PULLEIRO GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8993</v>
+        <v>0.5198</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4992</v>
+        <v>-1.89</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3985</v>
+        <v>2.4098</v>
       </c>
       <c r="G12" t="n">
-        <v>1.282</v>
+        <v>-2.4511</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2216</v>
+        <v>-2.8504</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0604</v>
+        <v>0.3993</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1759</v>
+        <v>-3.4822</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4903</v>
+        <v>-2.9212</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3144</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1061</v>
+        <v>1.0311</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2687</v>
+        <v>0.0708</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3749</v>
+        <v>0.9603</v>
       </c>
       <c r="P12" t="n">
         <v>1.3709</v>
@@ -1390,22 +1390,22 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8124</v>
+        <v>1.267</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9504</v>
+        <v>0.9839</v>
       </c>
       <c r="U12" t="n">
-        <v>0.138</v>
+        <v>0.283</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9412</v>
+        <v>0.3329</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="13">
@@ -1426,10 +1426,10 @@
         <v>57.5235</v>
       </c>
       <c r="E13" t="n">
-        <v>26.2132</v>
+        <v>26.2131</v>
       </c>
       <c r="F13" t="n">
-        <v>31.3105</v>
+        <v>31.3106</v>
       </c>
       <c r="G13" t="n">
         <v>35.2634</v>
@@ -1468,13 +1468,13 @@
         <v>19.5847</v>
       </c>
       <c r="S13" t="n">
-        <v>4.246400000000001</v>
+        <v>4.2463</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4439</v>
+        <v>1.4438</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8026</v>
+        <v>2.8024</v>
       </c>
       <c r="V13" t="n">
         <v>7.241999999999999</v>
@@ -1483,7 +1483,7 @@
         <v>11.0521</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.810099999999999</v>
+        <v>-3.8101</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8697</v>
+        <v>-1.4985</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3871</v>
+        <v>-0.4316</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2568</v>
+        <v>-1.0669</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7043</v>
@@ -1546,13 +1546,13 @@
         <v>0.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4979</v>
+        <v>-0.1309</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0081</v>
+        <v>0.1894</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5101</v>
+        <v>-0.3202</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0551</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.8679</v>
+        <v>-4.3633</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6679</v>
+        <v>-0.5601</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5358</v>
+        <v>-3.8031</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4635</v>
@@ -1624,13 +1624,13 @@
         <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1832</v>
+        <v>0.6878</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5585</v>
+        <v>0.3305</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6246</v>
+        <v>0.3573</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8249</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.5112</v>
+        <v>-4.9796</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.1789</v>
+        <v>-3.9976</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3324</v>
+        <v>-0.9821</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0246</v>
@@ -1702,13 +1702,13 @@
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5526</v>
+        <v>-1.021</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3723</v>
+        <v>-0.4464</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.5746</v>
       </c>
       <c r="V16" t="n">
         <v>-0.388</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.8002</v>
+        <v>-5.3033</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.6113</v>
+        <v>-4.3043</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.189</v>
+        <v>-0.9991</v>
       </c>
       <c r="G17" t="n">
         <v>-3.998</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2759</v>
+        <v>-0.779</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9745</v>
+        <v>-0.6675</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3014</v>
+        <v>-0.1114</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3304</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.9736</v>
+        <v>-5.3596</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.4504</v>
+        <v>-2.8363</v>
       </c>
       <c r="F18" t="n">
         <v>-2.5232</v>
@@ -1858,10 +1858,10 @@
         <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9022</v>
+        <v>-0.2882</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9745</v>
+        <v>-0.3605</v>
       </c>
       <c r="U18" t="n">
         <v>0.0723</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.034</v>
+        <v>-7.0183</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2946</v>
+        <v>-1.9876</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.7395</v>
+        <v>-5.0307</v>
       </c>
       <c r="G19" t="n">
         <v>-5.5252</v>
@@ -1936,13 +1936,13 @@
         <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4745</v>
+        <v>-0.4587</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7675</v>
+        <v>-0.4605</v>
       </c>
       <c r="U19" t="n">
-        <v>0.293</v>
+        <v>0.0018</v>
       </c>
       <c r="V19" t="n">
         <v>-0.0551</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.6803</v>
+        <v>-9.834899999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.76</v>
+        <v>-6.9413</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9203</v>
+        <v>-2.8936</v>
       </c>
       <c r="G21" t="n">
         <v>-7.0695</v>
@@ -2092,13 +2092,13 @@
         <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3355</v>
+        <v>-0.4901</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2892</v>
+        <v>-0.4705</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0463</v>
+        <v>-0.0196</v>
       </c>
       <c r="V21" t="n">
         <v>-1.492</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.9403</v>
+        <v>-10.6377</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.0383</v>
+        <v>-6.2196</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.902</v>
+        <v>-4.4181</v>
       </c>
       <c r="G22" t="n">
         <v>-7.5258</v>
@@ -2170,13 +2170,13 @@
         <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3802</v>
+        <v>-1.0776</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5445</v>
+        <v>-0.7258</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8358</v>
+        <v>-0.3518</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6634</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-57.5233</v>
+        <v>-56.8413</v>
       </c>
       <c r="E23" t="n">
-        <v>-31.3106</v>
+        <v>-31.3105</v>
       </c>
       <c r="F23" t="n">
-        <v>-26.213</v>
+        <v>-25.5308</v>
       </c>
       <c r="G23" t="n">
         <v>-35.2634</v>
@@ -2248,13 +2248,13 @@
         <v>8.812900000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.2463</v>
+        <v>-3.5642</v>
       </c>
       <c r="T23" t="n">
         <v>-2.8024</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4439</v>
+        <v>-0.7615</v>
       </c>
       <c r="V23" t="n">
         <v>-7.2421</v>
